--- a/example/19-flusso-acciaio-misto/archivio/REV002/Combo_REV002.xlsx
+++ b/example/19-flusso-acciaio-misto/archivio/REV002/Combo_REV002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\g.pacini\Documents\Repository\BridGHe\examples\19-flusso-acciaio-misto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1BBC7A5-F415-4B00-8899-6296E98CFFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40B06C5-D842-49EA-A6E4-9D77DF53091D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -416,7 +416,7 @@
         <v>1.5</v>
       </c>
       <c r="D2">
-        <v>1.3</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>0.9</v>
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>1.3</v>
@@ -470,7 +470,7 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -499,7 +499,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1.5</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>0</v>
